--- a/data/trans_dic/DC_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/DC_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,12; 41,21</t>
+          <t>33,57; 41,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56,03; 61,66</t>
+          <t>55,87; 61,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,71; 52,3</t>
+          <t>47,67; 52,34</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,88; 22,32</t>
+          <t>13,22; 22,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,41; 57,41</t>
+          <t>36,09; 59,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,07; 42,22</t>
+          <t>25,59; 40,74</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,07; 19,86</t>
+          <t>14,24; 20,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,49; 36,86</t>
+          <t>30,23; 36,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,18; 27,8</t>
+          <t>23,13; 27,72</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,73; 23,8</t>
+          <t>16,87; 23,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,33; 55,04</t>
+          <t>40,42; 54,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,81; 39,83</t>
+          <t>29,81; 39,37</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico (incluye Otro dolor crónico)</t>
+          <t>Población con dolor crónico (incluye Otro dolor crónico) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>170546; 212187</t>
+          <t>172840; 212679</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>423347; 465882</t>
+          <t>422083; 464422</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>606150; 664414</t>
+          <t>605636; 665008</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>317942; 511254</t>
+          <t>302841; 508312</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>792327; 1284690</t>
+          <t>807628; 1337089</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1180441; 1911631</t>
+          <t>1158747; 1844559</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>90998; 128446</t>
+          <t>92096; 129922</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>201344; 243419</t>
+          <t>199657; 243073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>303040; 363431</t>
+          <t>302294; 362333</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>577361; 821662</t>
+          <t>582504; 813866</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1473531; 2011005</t>
+          <t>1476708; 1988583</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2118321; 2830440</t>
+          <t>2118359; 2797662</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/DC_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/DC_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,25%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,57; 41,3</t>
+          <t>32,03; 39,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,87; 61,47</t>
+          <t>56,02; 61,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,67; 52,34</t>
+          <t>46,83; 51,57</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,22; 22,19</t>
+          <t>19,53; 23,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,09; 59,75</t>
+          <t>34,17; 37,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,59; 40,74</t>
+          <t>27,15; 29,98</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,24; 20,09</t>
+          <t>14,12; 19,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,23; 36,8</t>
+          <t>30,83; 37,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,13; 27,72</t>
+          <t>23,39; 27,87</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,87; 23,58</t>
+          <t>21,35; 24,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,42; 54,43</t>
+          <t>39,17; 41,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,81; 39,37</t>
+          <t>31,0; 33,08</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>192378</t>
+          <t>206748</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>444551</t>
+          <t>483088</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>636929</t>
+          <t>689835</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>172840; 212679</t>
+          <t>185330; 228230</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>422083; 464422</t>
+          <t>460512; 504583</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>605636; 665008</t>
+          <t>655921; 722264</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>441162</t>
+          <t>477496</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>963255</t>
+          <t>779539</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1404417</t>
+          <t>1257036</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>302841; 508312</t>
+          <t>435723; 519571</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>807628; 1337089</t>
+          <t>741949; 823707</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1158747; 1844559</t>
+          <t>1195314; 1319782</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>110053</t>
+          <t>120718</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>222877</t>
+          <t>249443</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>332930</t>
+          <t>370161</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>92096; 129922</t>
+          <t>100466; 141017</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>199657; 243073</t>
+          <t>226537; 273835</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>302294; 362333</t>
+          <t>338258; 403089</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>743594</t>
+          <t>804962</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1630683</t>
+          <t>1512070</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2374277</t>
+          <t>2317032</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>582504; 813866</t>
+          <t>751680; 856982</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1476708; 1988583</t>
+          <t>1460343; 1565583</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2118359; 2797662</t>
+          <t>2247390; 2397803</t>
         </is>
       </c>
     </row>
